--- a/output/第10期計画_資料提供依頼_第9期の施策事業実績.xlsx
+++ b/output/第10期計画_資料提供依頼_第9期の施策事業実績.xlsx
@@ -14,6 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_基盤整備の実績" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_決算の状況" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_提供が難しい場合" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_見える化での代替可能性" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_交付金指標による暫定代替" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +64,10 @@
       <name val="游ゴシック"/>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -210,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -259,6 +265,19 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5165,22 +5184,22 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>代替できません。見える化システム・給付実績はサービスの利用実績であり、地域支援事業や普及啓発等の事業量は含みません。</t>
+          <t>見える化システムでは代替できません。見える化システム・給付実績はサービスの利用実績であり、地域支援事業や普及啓発等の事業量は含みません。取組の有無に限っては、交付金評価の大項目別得点（07・08シート）で部分的に代替できます。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>第9期のプロセス評価ができません。「計画に定めた事業が実施されたか」を記述できず、第3章は成果（代表KPI）と外部評価（交付金）のみの評価となります。</t>
+          <t>事業量と対象実人数は得られません。交付金評価は国の様式に沿った53項目であり、第9期計画の19施策と1対1で対応しません。また得点0が取組の不在によるものか、取組はあったが国の要件を満たさなかったものかを判別できません。</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>第3章第5節に「事業の実施状況は資料が得られなかったため評価していない」と明記します。</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>第3章第5節に「事業量・対象実人数は資料が得られなかったため評価していない」と明記し、交付金の大項目別得点による取組状況の整理を併記します。</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>一部可</t>
         </is>
       </c>
     </row>
@@ -5225,22 +5244,22 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの通いの場の系列で代替できる可能性があります。ただし当広域連合のデータ登録状況を確認する必要があります。</t>
+          <t>見える化システムのF1〜F9を受領済みですが、収録は令和2年度までで、令和3年度以降は登録がないことを確認しています（令和8年7月29日）。令和6〜8年度は代替できません。</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>登録がない場合は代替できません。国の目標値8％との比較ができず、第9期の代表KPI④の評価が自己申告割合のみとなります。</t>
+          <t>第9期（令和6〜8年度）の通いの場の実績が得られません。国の目標値8％との比較ができず、第9期の代表KPI④の評価が自己申告割合のみとなります。</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>第3章第1節に、国の目標値と統計が異なるため直接比較できない旨を記載します（記載済み）。</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3章第1節に、国の目標値と統計が異なるため直接比較できない旨と、総合事業ベースの最新値が令和2年度である旨を記載します。</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
@@ -5379,4 +5398,4073 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>見える化システムで代替できるか（01シートの14項目の逐条確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="56" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>01シートの14項目について、地域包括ケア「見える化」システムで代替できるかを1項目ずつ確認した結果です。見える化システムは介護保険事業状況報告・介護給付費等実態統計等を集約したものであり、サービスの利用実績と保険者の体制を扱います。施策・事業の実施実績（何を何回行い、何人が参加したか）は収録の対象外です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>依頼する資料（01シートの項目）</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>対応する系列</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>系列の収録年度</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>確認した結果</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>残る手当て</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>代替の可否</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="88" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>19施策に対応する事業の実施状況</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>見える化に施策・事業の実施状況を扱う系列はありません。最も近いのは交付金の評価指標（W系列）ですが、見える化のW系列は総合得点と目標別・指標群別の小計にとどまります。</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>令和8年8月28日に受領した交付金の全国集計結果には大項目別（53項目）の得点まで収録されており、3町×3か年で公表の合計と完全に一致することを確認しました（08シート）。取組の有無に限り、これで暫定的に代替します。</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>一部可</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>各事業の事業量（実施回数・開催回数等）</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>見える化はサービスの利用実績（受給者数・給付費・回数）を扱いますが、これは介護給付の対象となるサービスの実績です。地域支援事業の事業量、普及啓発、研修、会議の開催回数は含みません。</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>代替できません。ご提供が必要です。</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>各事業の対象実人数</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>同上。加えて見える化の人数は延べ又は月平均の受給者数であり、事業ごとの対象実人数を取り出すことはできません。</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>代替できません。ご提供が必要です。</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>各事業の予算額・決算額</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>見える化の給付費は保険給付費であり、事業別の予算・決算ではありません。</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>款レベルは地方財政状況調査で代替できますが、事業別の内訳は代替できません。</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>総合事業の実績（訪問型・通所型ほか5区分）</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>F1〜F9</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>平成25年度〜令和2年度</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>F系列は受領済みですが、収録は令和2年度までです。令和3年度以降は当広域連合について登録がないことを確認しています（令和8年7月29日）。第9期（令和6〜8年度）の実績は含まれません。</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>国が公表する「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和3年度以降の集計、又は保険者が国へ報告した調査票の写しのご提供が必要です。</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>包括的支援事業の実績（6事業）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>見える化に包括的支援事業の実績を扱う系列はありません。地域包括支援センターに関する系列としては、交付金の活動指標「地域包括支援センター３職種の配置状況」「地域包括支援センター事業評価の達成状況」があるのみです。</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>相談件数・実人数・会議回数は代替できません。ご提供が必要です。</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>任意事業の実績</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>見える化に任意事業の実績を扱う系列はありません。</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>給付適正化の取組の有無は交付金の大項目「給付費適正化方策の策定状況」「給付費適正化事業の取組状況」「ケアプラン点検の実施状況」「医療情報との突合の実施状況」で把握できます（08シート）。事業費と件数は代替できません。</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>一部可</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>通いの場の箇所数・参加実人数</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>F1〜F9</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>平成25年度〜令和2年度</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>F1・F2・F3（週1回以上の参加率・参加者数・箇所数）、F4・F5（月1回以上の参加率・参加者数）、F7〜F9（運営主体別・活動場所別・活動内容別の箇所数）を受領済みですが、令和2年度が最新です。令和2年度の値は月1回以上1.6％・週1回以上3箇所で、平成29年度（3.1％・7箇所）から低下しています。</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>令和6〜8年度は代替できません。交付金の活動指標「通いの場への参加率」の得点（令和8年度 東川町0／美瑛町0／東神楽町4）から水準の目安は得られますが、箇所数と参加実人数は得られません。</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画の整備予定量と実際の整備</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>K1〜K3</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>平成24年度〜令和6年度</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>K系列（サービス提供事業所数）を全28種別受領済みで、令和6年度まで収録されています。事業所数の増減は把握できます。定員は収録されていません。</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>令和7・8年度と定員は、北海道が公表する指定等の異動一覧及び介護保険事業所一覧（受領済み）で補います。整備を予定したが実現しなかった理由は代替できません。</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>一部可</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>事業所の新規指定・廃止・休止の記録</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>K1〜K3</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>平成24年度〜令和6年度</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>K系列は年度末の事業所数であり、異動の時期と事由は分かりません。</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>北海道の指定等の異動一覧（受領済み）で新規・廃止・休止は把握できます。事由は代替できません。</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>一部可</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>介護保険特別会計の歳入歳出決算額</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>C1（必要保険料月額）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>第1期〜第9期</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>見える化の必要保険料月額は保険給付費と地域支援事業費から算定される推計であり、決算額そのものではありません。</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>款レベルの決算額は地方財政状況調査（決算状況調）で代替できます。項・目レベルと事業別の決算額は代替できません。</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>一部可</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>介護給付費準備基金の積立・取崩と残高</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>見える化に基金の系列はありません。公表資料からも得られません。</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>代替できません。ご提供が必要です。第10期の保険料算定における取崩額の設定に直結します。</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>介護保険運営協議会の開催記録と付議事項</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>見える化に会議の開催記録を扱う系列はありません。交付金の大項目「事業計画の進捗状況」「評価結果の活用」が近い内容を評価していますが、開催記録そのものではありません。</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>代替できません。ご提供が必要です。</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画の自己評価・北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>見える化に該当する系列はありません。交付金の大項目「施策の実施状況の把握・改善」（令和8年度 東川町4／美瑛町8／東神楽町16、配点16）が、自己評価の実施状況を国の要件で評価した唯一の外部データです。</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>評価の内容と北海道への報告文書は代替できません。ご提供が必要です。</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>一部可</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>【まとめ】</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>代替できる（可）</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>見える化のみで足りる項目はありません。</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>一部代替できる（一部可）</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>5件</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>No.1・7・9・10・11・14。取組の有無、事業所数の増減、款レベルの決算額は代替できますが、事業量・対象実人数・事業費は代替できません。</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>代替できない（不可）</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>8件</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>No.2・3・4・5・6・8・12・13。とくにNo.5・No.6（地域支援事業の実績）とNo.12（基金）は、ご提供いただかないと計画本文が空欄のままとなります。</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="10" t="n"/>
+    </row>
+    <row r="26" ht="118" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>注1）見える化システムは、介護保険事業状況報告・介護給付費等実態統計・国勢調査等を集約したものです。収録されるのは介護給付の対象となるサービスの利用実績と保険者の体制であり、施策・事業をどれだけ実施したかという実績は収録の対象外です。したがって、資料No.13の中心である02シート（施策別の実績）と03シート（地域支援事業の実績）は、見える化では代替できないという結論になります。注2）当広域連合について登録がなく出力できない系列は、δ（自給率）・H1/H2（介護人材の必要数）・J（認知症施策）・L（医療機関・看取り）です（令和8年7月29日に確認済み）。F系列は登録がありますが令和2年度までです。注3）代替による場合は、その旨と限界を計画本文の注記に明記し、計画素案の別管理表に記録します。後日ご提供いただいた実績値と置き換えます。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C22:G22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の大項目別得点（3町・3か年）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="56" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>資料No.13が受領できるまでの暫定の代替として、交付金評価の大項目別得点を整理しました。令和8年8月28日に受領した全国集計結果には明細まで得点が入っており、大項目単位で合算すると公表の推進・支援合計と3町×3か年の9通りすべてで一致することを確認しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>令和6年度</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>交付金</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>目標</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>指標群</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>大項目</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>得点0の年度・町</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>地域の介護保険事業の特徴</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="I6" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="J6" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="K6" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="L6" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="M6" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="N6" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>事業計画の進捗状況</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="N7" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="P7" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>施策の実施状況の把握・改善</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="I8" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="L8" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="N8" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="P8" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>評価結果の活用</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t>収録された3か年とも3町すべて0点</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>今年度の評価点</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="23" t="inlineStr">
+        <is>
+          <t>収録された3か年とも3町すべて0点</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>後期高齢者と給付費の伸び率比較</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="L11" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="M11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="P11" s="23" t="inlineStr">
+        <is>
+          <t>R6美瑛・R7美瑛・R8美瑛</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>PFS委託事業数</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="23" t="inlineStr">
+        <is>
+          <t>収録された3か年とも3町すべて0点</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅱ</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>給付費適正化方策の策定状況</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H13" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="M13" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="N13" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅱ</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>給付費適正化事業の取組状況</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="H14" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="L14" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="N14" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅱ</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>ケアプラン点検の実施状況</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>収録された3か年とも3町すべて0点</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅱ</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>医療情報との突合の実施状況</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="J16" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="K16" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="L16" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="M16" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="N16" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="P16" s="23" t="inlineStr">
+        <is>
+          <t>R6東川・R6美瑛・R6東神</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅲ</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>介護人材の確保・定着の取組状況</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="G17" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="H17" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="J17" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="K17" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="M17" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="N17" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="P17" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅲ</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>庁内・庁外における連携体制</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="G18" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="I18" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="J18" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="K18" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="L18" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="M18" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="N18" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="P18" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅲ</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>介護の仕事の魅力に関する研修の実施状況</t>
+        </is>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="23" t="inlineStr">
+        <is>
+          <t>収録された3か年とも3町すべて0点</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅲ</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>介護人材の定着・資質向上に関する研修の実施状況</t>
+        </is>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="23" t="inlineStr">
+        <is>
+          <t>収録された3か年とも3町すべて0点</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅲ</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>介護支援専門員に対する研修の実施状況</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="23" t="inlineStr">
+        <is>
+          <t>R6美瑛・R6東神・R7美瑛・R7東神・R8美瑛・R8東神</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅳ</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>成果指標群</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>短期的な要介護度の変化（要介護１・２）</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="G22" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="I22" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="J22" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="K22" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="L22" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="23" t="inlineStr">
+        <is>
+          <t>R8東川・R8美瑛・R8東神</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅳ</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>成果指標群</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>長期的な要介護度の変化（要介護１・２）</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="G23" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="I23" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="K23" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L23" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="M23" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="N23" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="P23" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅳ</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>成果指標群</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>短期的な要介護度の変化（要介護３～５）</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="M24" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="N24" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="P24" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅳ</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>成果指標群</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>長期的な要介護度の変化（要介護３～５）</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="G25" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="I25" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="K25" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L25" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="M25" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="P25" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>推進</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅳ</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>成果指標群</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>健康寿命延伸の状況</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="J26" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="K26" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="L26" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="M26" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N26" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="P26" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>データを活用した課題の把握</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N27" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="P27" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>アウトリーチ等の取組状況</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="L28" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="P28" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>介護予防等と保健事業の一体的実施</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="I29" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="L29" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M29" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="P29" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>通いの場参加者の健康状態の把握・分析</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="L30" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M30" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="P30" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>地域リハビリテーションの推進</t>
+        </is>
+      </c>
+      <c r="F31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="L31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N31" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="P31" s="23" t="inlineStr">
+        <is>
+          <t>R6東川・R7東川・R8東川</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>介護予防・生活支援の体制整備</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L32" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N32" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>多様なサービスの活用推進</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M33" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N33" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>地域包括支援センター３職種の配置状況</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L34" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M34" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P34" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>地域包括支援センター事業評価の達成状況</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L35" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>個別事例の検討割合</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N36" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P36" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>通いの場への参加率</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I37" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="L37" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P37" s="23" t="inlineStr">
+        <is>
+          <t>R6美瑛・R7美瑛・R8東川・R8美瑛</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>ポイント事業への参加率</t>
+        </is>
+      </c>
+      <c r="F38" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" s="23" t="inlineStr">
+        <is>
+          <t>R6東川・R6東神・R7東川・R8東川</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>心身・認知機能維持・改善者の割合</t>
+        </is>
+      </c>
+      <c r="F39" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N39" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P39" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>生活支援コーディネーター数</t>
+        </is>
+      </c>
+      <c r="F40" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H40" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M40" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N40" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P40" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>生活支援コーディネーターの地域ケア会議への参加割合</t>
+        </is>
+      </c>
+      <c r="F41" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G41" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J41" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M41" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N41" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P41" s="23" t="inlineStr">
+        <is>
+          <t>R6東神</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>多様なサービスの実施状況</t>
+        </is>
+      </c>
+      <c r="F42" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H42" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K42" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L42" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M42" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N42" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P42" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅱ</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>認知症サポーター等を活用した地域支援体制の構築</t>
+        </is>
+      </c>
+      <c r="F43" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="I43" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L43" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="M43" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N43" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P43" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅱ</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>早期診断・早期対応の体制構築</t>
+        </is>
+      </c>
+      <c r="F44" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="G44" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="H44" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="I44" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="J44" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="K44" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="L44" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="M44" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="N44" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="P44" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅱ</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>難聴高齢者の早期発見・早期介入</t>
+        </is>
+      </c>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="22" t="n"/>
+      <c r="H45" s="22" t="n"/>
+      <c r="I45" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="J45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L45" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="M45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="P45" s="23" t="inlineStr">
+        <is>
+          <t>R7美瑛・R8美瑛</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅱ</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>活動指標群</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>認知症サポーター数</t>
+        </is>
+      </c>
+      <c r="F46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="K46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="N46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="23" t="inlineStr">
+        <is>
+          <t>R6東川・R6東神・R7東川・R7東神・R8東川・R8東神</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅱ</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>活動指標群</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>認知症サポーターステップアップ講座修了者数</t>
+        </is>
+      </c>
+      <c r="F47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="23" t="inlineStr">
+        <is>
+          <t>収録された3か年とも3町すべて0点</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅱ</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>活動指標群</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>認知症地域支援推進員の業務の状況</t>
+        </is>
+      </c>
+      <c r="F48" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="J48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="L48" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="M48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="P48" s="23" t="inlineStr">
+        <is>
+          <t>R6美瑛・R6東神・R7美瑛・R8美瑛</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅲ</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>在宅医療・介護連携に関する課題・対応策の検討</t>
+        </is>
+      </c>
+      <c r="F49" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="G49" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="H49" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="I49" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="J49" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="K49" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="L49" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="M49" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="N49" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="P49" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅲ</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>在宅医療・介護連携の具体的取組状況</t>
+        </is>
+      </c>
+      <c r="F50" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G50" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="H50" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I50" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J50" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K50" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L50" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M50" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="N50" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="P50" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅲ</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>医療・介護関係者間の情報共有</t>
+        </is>
+      </c>
+      <c r="F51" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H51" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="I51" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="L51" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M51" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="N51" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="P51" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅲ</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>入退院支援の実施状況</t>
+        </is>
+      </c>
+      <c r="F52" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M52" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N52" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P52" s="23" t="inlineStr">
+        <is>
+          <t>R6東川・R6美瑛・R6東神・R7東川・R7美瑛・R7東神</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅲ</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>（ⅱ）活動指標群</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>人生の最終段階における支援の実施状況</t>
+        </is>
+      </c>
+      <c r="F53" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="L53" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="P53" s="23" t="inlineStr">
+        <is>
+          <t>R6東川・R6美瑛・R6東神・R7美瑛・R8美瑛</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅳ</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>成果指標群</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>短期的な要介護度の変化（要介護１・２）</t>
+        </is>
+      </c>
+      <c r="F54" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="G54" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="H54" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="I54" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="J54" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="K54" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="L54" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="23" t="inlineStr">
+        <is>
+          <t>R8東川・R8美瑛・R8東神</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅳ</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>成果指標群</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>長期的な要介護度の変化（要介護１・２）</t>
+        </is>
+      </c>
+      <c r="F55" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="G55" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="H55" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="I55" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="J55" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="K55" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L55" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="M55" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="N55" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="P55" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅳ</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>成果指標群</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>短期的な要介護度の変化（要介護３～５）</t>
+        </is>
+      </c>
+      <c r="F56" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="G56" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H56" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="I56" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J56" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L56" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="M56" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="N56" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="P56" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅳ</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>成果指標群</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>長期的な要介護度の変化（要介護３～５）</t>
+        </is>
+      </c>
+      <c r="F57" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="G57" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="H57" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="I57" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="J57" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="K57" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L57" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="M57" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N57" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="P57" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅳ</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>成果指標群</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>健康寿命延伸の状況</t>
+        </is>
+      </c>
+      <c r="F58" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G58" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H58" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I58" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="J58" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="K58" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="L58" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="M58" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N58" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="P58" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>支援</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅱ</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>目標Ⅱｰ（ⅰ）体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>認知症初期集中支援チームの活動状況</t>
+        </is>
+      </c>
+      <c r="F59" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="G59" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="I59" s="22" t="n"/>
+      <c r="J59" s="22" t="n"/>
+      <c r="K59" s="22" t="n"/>
+      <c r="L59" s="22" t="n"/>
+      <c r="M59" s="22" t="n"/>
+      <c r="N59" s="22" t="n"/>
+      <c r="P59" s="23" t="inlineStr">
+        <is>
+          <t>R6美瑛</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>【この表から読み取れること】</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>事項</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr"/>
+      <c r="J62" s="4" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr"/>
+      <c r="L62" s="4" t="inlineStr"/>
+      <c r="M62" s="4" t="inlineStr"/>
+      <c r="N62" s="4" t="inlineStr"/>
+      <c r="O62" s="4" t="inlineStr"/>
+      <c r="P62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63" ht="76" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>3か年を通じて3町とも0点の大項目（7項目）</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>推進「評価結果の活用」「今年度の評価点」「PFS委託事業数」「ケアプラン点検の実施状況」「介護の仕事の魅力に関する研修の実施状況」「介護人材の定着・資質向上に関する研修の実施状況」、支援「認知症サポーターステップアップ講座修了者数」。これらは第10期で新たに取り組むべき候補です。ただし取組の不在によるものか、国の要件を満たさなかったものかは判別できません。この判別のためにも資料No.13が必要です。</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n"/>
+      <c r="E63" s="9" t="n"/>
+      <c r="F63" s="9" t="n"/>
+      <c r="G63" s="9" t="n"/>
+      <c r="H63" s="9" t="n"/>
+      <c r="I63" s="9" t="n"/>
+      <c r="J63" s="9" t="n"/>
+      <c r="K63" s="9" t="n"/>
+      <c r="L63" s="9" t="n"/>
+      <c r="M63" s="9" t="n"/>
+      <c r="N63" s="9" t="n"/>
+      <c r="O63" s="9" t="n"/>
+      <c r="P63" s="10" t="n"/>
+    </row>
+    <row r="64" ht="76" customHeight="1">
+      <c r="A64" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>3町で差がある大項目</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>「施策の実施状況の把握・改善」（令和8年度 4／8／16）、「難聴高齢者の早期発見・早期介入」（10／0／10）、「人生の最終段階における支援の実施状況」（2／0／12）、「通いの場への参加率」（0／0／4）。保険者は広域連合ですが、交付金の評価は町ごとに行われており、取組の実施主体が町であることを示しています。</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n"/>
+      <c r="E64" s="9" t="n"/>
+      <c r="F64" s="9" t="n"/>
+      <c r="G64" s="9" t="n"/>
+      <c r="H64" s="9" t="n"/>
+      <c r="I64" s="9" t="n"/>
+      <c r="J64" s="9" t="n"/>
+      <c r="K64" s="9" t="n"/>
+      <c r="L64" s="9" t="n"/>
+      <c r="M64" s="9" t="n"/>
+      <c r="N64" s="9" t="n"/>
+      <c r="O64" s="9" t="n"/>
+      <c r="P64" s="10" t="n"/>
+    </row>
+    <row r="65" ht="76" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>第9期の期間中に改善した大項目</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>各町の令和6年度から令和8年度への得点の変化から読み取れます。総合得点は東川町316→315、美瑛町312→308、東神楽町368→379で、大きな変化はありません。</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n"/>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="9" t="n"/>
+      <c r="G65" s="9" t="n"/>
+      <c r="H65" s="9" t="n"/>
+      <c r="I65" s="9" t="n"/>
+      <c r="J65" s="9" t="n"/>
+      <c r="K65" s="9" t="n"/>
+      <c r="L65" s="9" t="n"/>
+      <c r="M65" s="9" t="n"/>
+      <c r="N65" s="9" t="n"/>
+      <c r="O65" s="9" t="n"/>
+      <c r="P65" s="10" t="n"/>
+    </row>
+    <row r="66" ht="76" customHeight="1">
+      <c r="A66" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>評価指標の入替え</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>国の評価指標は年度により入れ替わります。「認知症初期集中支援チームの活動状況」は令和6年度限りで、令和7年度から「難聴高齢者の早期発見・早期介入」に替わっています。時系列で比較する際はこの入替えにご留意ください。</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n"/>
+      <c r="E66" s="9" t="n"/>
+      <c r="F66" s="9" t="n"/>
+      <c r="G66" s="9" t="n"/>
+      <c r="H66" s="9" t="n"/>
+      <c r="I66" s="9" t="n"/>
+      <c r="J66" s="9" t="n"/>
+      <c r="K66" s="9" t="n"/>
+      <c r="L66" s="9" t="n"/>
+      <c r="M66" s="9" t="n"/>
+      <c r="N66" s="9" t="n"/>
+      <c r="O66" s="9" t="n"/>
+      <c r="P66" s="10" t="n"/>
+    </row>
+    <row r="67" ht="76" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>この表で代替できないこと</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>事業量・対象実人数・決算額は含まれません。また国の評価指標の項目であり、第9期計画の19施策と1対1で対応しません。資料No.13の02・03シートの代わりにはなりません。</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n"/>
+      <c r="E67" s="9" t="n"/>
+      <c r="F67" s="9" t="n"/>
+      <c r="G67" s="9" t="n"/>
+      <c r="H67" s="9" t="n"/>
+      <c r="I67" s="9" t="n"/>
+      <c r="J67" s="9" t="n"/>
+      <c r="K67" s="9" t="n"/>
+      <c r="L67" s="9" t="n"/>
+      <c r="M67" s="9" t="n"/>
+      <c r="N67" s="9" t="n"/>
+      <c r="O67" s="9" t="n"/>
+      <c r="P67" s="10" t="n"/>
+    </row>
+    <row r="69" ht="96" customHeight="1">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>注1）出典は厚生労働省「保険者機能強化推進交付金等（市町村分）に係る全国集計結果」令和6年度・令和7年度・令和8年度（令和8年8月28日受領）です。注2）成果指標群（目標Ⅳ）は推進・支援の両交付金で共通のため、同じ大項目が2行に現れます。注3）配点欄は設けていません。成果指標群は選択肢が排他的であり、明細の配点の合計が満点（100点）を超えるためです。得点は推移と町間の比較にご覧ください。注4）本表は資料No.13が受領できるまでの暫定の整理です。受領後は実績値に置き換え、置き換えた箇所を別管理表に記録します。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="C64:P64"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A61:P61"/>
+    <mergeCell ref="C67:P67"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="C63:P63"/>
+    <mergeCell ref="C65:P65"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="A69:P69"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="C66:P66"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/第10期計画_資料提供依頼_第9期の施策事業実績.xlsx
+++ b/output/第10期計画_資料提供依頼_第9期の施策事業実績.xlsx
@@ -5214,17 +5214,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告（厚生労働省が公表）の広域連合分により、事業費と一部の実施状況は代替できます。</t>
+          <t>令和6年度分は、総合事業の実施状況に関する調査により総合事業と一般介護予防事業を代替できます（令和8年8月28日受領・別途点検結果を作成）。事業費は介護保険事業状況報告の広域連合分で代替できます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>参加実人数と町別の内訳が得られません。代表KPI H05の分子を確定できません。</t>
+          <t>令和7・8年度は代替できません。また同調査の対象は総合事業と一般介護予防事業であり、包括的支援事業6事業と任意事業の実績は含まれません。</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>第3章第2節に事業費のみを記載し、実人数は「把握していない」と注記します。</t>
+          <t>第3章第2節に令和6年度の実績を記載し、令和7・8年度と包括的支援事業・任意事業は「資料が得られていない」と注記します。</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -5244,22 +5244,22 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>見える化システムのF1〜F9を受領済みですが、収録は令和2年度までで、令和3年度以降は登録がないことを確認しています（令和8年7月29日）。令和6〜8年度は代替できません。</t>
+          <t>令和6年度分は、総合事業の実施状況に関する調査により確定しました（令和8年8月28日受領）。3町計25箇所・330人、うち週1回以上11箇所・120人です。見える化F1〜F9は令和2年度までで、令和3〜5年度は空白のままです。</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6〜8年度）の通いの場の実績が得られません。国の目標値8％との比較ができず、第9期の代表KPI④の評価が自己申告割合のみとなります。</t>
+          <t>令和7・8年度は代替できません。令和3〜5年度が空白のため、令和2年度から令和6年度への推移の経過は分かりません。</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>第3章第1節に、国の目標値と統計が異なるため直接比較できない旨と、総合事業ベースの最新値が令和2年度である旨を記載します。</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>第3章第1節に令和6年度の実績と国の目標8.0％との差を記載し、日常生活圏域ニーズ調査とは統計が異なる旨を併記します。</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>一部可</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5386,7 @@
     <row r="13" ht="96" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>注1）「不可」の3件（No.1・No.6・No.7）は、ご提供いただかないと計画本文の記述が空白のままとなります。とくにNo.1は、仕様書４（2）「第9期計画の評価・検証」の中心的な内容です。注2）代替手段による場合は、その旨と限界を計画本文の注記に明記し、計画素案の別管理表に記録します。注3）代替手段によって得られた値は、後日ご提供いただいた実績値と置き換えます。置き換えた箇所は別管理表に記録します。</t>
+          <t>注1）「不可」の2件（No.6・No.7）は、ご提供いただかないと計画本文の記述が空白のままとなります。また「一部可」のNo.1（施策ごとの事業量・対象実人数）は、仕様書４（2）「第9期計画の評価・検証」の中心的な内容であり、交付金指標では取組の有無しか代替できません。注2）代替手段による場合は、その旨と限界を計画本文の注記に明記し、計画素案の別管理表に記録します。注3）代替手段によって得られた値は、後日ご提供いただいた実績値と置き換えます。置き換えた箇所は別管理表に記録します。</t>
         </is>
       </c>
     </row>
@@ -5620,27 +5620,30 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>F1〜F9</t>
+          <t>F1〜F9
+（調査本体を
+直接受領）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>平成25年度〜令和2年度</t>
+          <t>F系列は令和2年度まで
+調査本体は令和6年度</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>F系列は受領済みですが、収録は令和2年度までです。令和3年度以降は当広域連合について登録がないことを確認しています（令和8年7月29日）。第9期（令和6〜8年度）の実績は含まれません。</t>
+          <t>見える化F系列は令和2年度までですが、その原典である「総合事業の実施状況に関する調査」の令和6年度分（市町村Ⅰ・Ⅱ・Ⅲ）を令和8年8月28日に受領しました。サービス種別ごとの実施の有無・事業所数・利用者実人数・延べ人数が町別に確定しています。</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>国が公表する「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和3年度以降の集計、又は保険者が国へ報告した調査票の写しのご提供が必要です。</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>令和7・8年度分は未受領です。令和3〜5年度も空白のままです。第9期の3か年を通した評価には令和7年度分が必要です。</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>一部可</t>
         </is>
       </c>
     </row>
@@ -5725,27 +5728,30 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>F1〜F9</t>
+          <t>F1〜F9
+（調査本体を
+直接受領）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>平成25年度〜令和2年度</t>
+          <t>F系列は令和2年度まで
+調査本体は令和6年度</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>F1・F2・F3（週1回以上の参加率・参加者数・箇所数）、F4・F5（月1回以上の参加率・参加者数）、F7〜F9（運営主体別・活動場所別・活動内容別の箇所数）を受領済みですが、令和2年度が最新です。令和2年度の値は月1回以上1.6％・週1回以上3箇所で、平成29年度（3.1％・7箇所）から低下しています。</t>
+          <t>調査本体の令和6年度分により確定しました。3町計25箇所・参加者実人数330人、うち週1回以上が11箇所・120人（いずれも東神楽町）です。令和2年度（週1回以上3箇所・月1回以上1.6％）から改善しています。代表KPI H05の総合事業ベースの基準値は令和6年度3.53％となります。</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>令和6〜8年度は代替できません。交付金の活動指標「通いの場への参加率」の得点（令和8年度 東川町0／美瑛町0／東神楽町4）から水準の目安は得られますが、箇所数と参加実人数は得られません。</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>令和7・8年度分は未受領です。令和3〜5年度が空白のため、増加した時期は分かりません。</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>一部可</t>
         </is>
       </c>
     </row>
@@ -6016,12 +6022,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>5件</t>
+          <t>8件</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>No.1・7・9・10・11・14。取組の有無、事業所数の増減、款レベルの決算額は代替できますが、事業量・対象実人数・事業費は代替できません。</t>
+          <t>No.1・5・7・8・9・10・11・14。No.5・No.8は、見える化F系列の原典である「総合事業の実施状況に関する調査」の令和6年度分を令和8年8月28日に受領したことにより、「不可」から「一部可」に改めました（令和7・8年度分は未受領）。</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
@@ -6037,12 +6043,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>8件</t>
+          <t>6件</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>No.2・3・4・5・6・8・12・13。とくにNo.5・No.6（地域支援事業の実績）とNo.12（基金）は、ご提供いただかないと計画本文が空欄のままとなります。</t>
+          <t>No.2・3・4・6・12・13。とくにNo.6（包括的支援事業の実績）とNo.12（基金）は、ご提供いただかないと計画本文が空欄のままとなります。</t>
         </is>
       </c>
       <c r="D24" s="9" t="n"/>
